--- a/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 13,3</t>
+          <t>-12,02; 13,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 6,43</t>
+          <t>-11,11; 6,48</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 12,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 8,69</t>
+          <t>-12,99; 8,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 28,88</t>
+          <t>-2,99; 29,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,56; 12,26</t>
+          <t>-10,89; 11,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-31,31; 0,0</t>
+          <t>-28,84; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 8,3</t>
+          <t>-3,38; 6,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,39</t>
+          <t>-3,05; 6,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 4,02</t>
+          <t>-4,63; 4,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,67; 21,59</t>
+          <t>2,65; 24,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,65; 0,0</t>
+          <t>-9,71; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-41,82; -4,51</t>
+          <t>-37,32; -4,45</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 6,45</t>
+          <t>-0,87; 6,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,39</t>
+          <t>-3,74; 1,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 1,79</t>
+          <t>-3,14; 1,55</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-40,62; 767,76</t>
+          <t>-39,41; 828,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-85,71; 134,07</t>
+          <t>-85,74; 96,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-95,59; 330,35</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,02; 13,3</t>
+          <t>-12,35; 13,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 6,48</t>
+          <t>-11,68; 6,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,48</t>
+          <t>0,0; 14,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 8,9</t>
+          <t>-12,64; 9,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 29,83</t>
+          <t>-2,99; 28,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 11,92</t>
+          <t>-10,86; 12,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,84; 0,0</t>
+          <t>-34,82; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,36</t>
+          <t>-3,44; 6,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 6,69</t>
+          <t>-3,6; 6,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 4,01</t>
+          <t>-4,9; 4,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 24,11</t>
+          <t>2,68; 24,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,71; 0,0</t>
+          <t>-10,69; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,32; -4,45</t>
+          <t>-37,82; -4,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 6,48</t>
+          <t>-0,97; 6,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 1,4</t>
+          <t>-3,9; 1,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 1,55</t>
+          <t>-3,25; 1,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-39,41; 828,87</t>
+          <t>-50,58; 583,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-85,74; 96,49</t>
+          <t>-87,71; 112,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-95,59; 330,35</t>
+          <t>-87,85; 372,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
@@ -520,7 +520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para los vómitos</t>
+          <t>Menores que consumieron medicamentos para los vómitos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,35; 13,41</t>
+          <t>-9,55; 13,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 6,47</t>
+          <t>-11,03; 6,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,86</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,64; 9,28</t>
+          <t>-12,91; 8,69</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 28,06</t>
+          <t>-2,98; 28,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 12,19</t>
+          <t>-7,56; 12,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 0,0</t>
+          <t>-31,31; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 6,76</t>
+          <t>-3,36; 8,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 6,38</t>
+          <t>-3,38; 6,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 4,03</t>
+          <t>-4,56; 4,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -954,12 +954,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,68; 24,05</t>
+          <t>2,67; 21,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 0,0</t>
+          <t>-9,65; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-37,82; -4,43</t>
+          <t>-41,82; -4,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 6,55</t>
+          <t>-1,01; 6,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 1,57</t>
+          <t>-4,23; 1,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 1,69</t>
+          <t>-2,93; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-50,58; 583,82</t>
+          <t>-40,62; 767,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-87,71; 112,74</t>
+          <t>-85,71; 134,07</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-87,85; 372,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP16A09-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,129 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+      <c r="C4" s="5" t="n">
+        <v>-0.4417269011931999</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>-0.323309312265839</v>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-9,55; 13,3</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.427599486297279</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1.466806292180742</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-0,47</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3,07</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-0,56</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-13,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-8,88%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-11,03; 6,43</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 14,97</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-12,91; 8,69</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-0.05181628480003218</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.8434292407611798</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-0.1504477253269952</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.06881621352394458</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1212140077843879</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7,75</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,94</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>264,8%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.992074551255399</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.582724519841634</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-2,98; 28,88</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-7,56; 12,26</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-31,31; 0,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>1.405820745084249</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.220398577227801</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.689478138608255</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr"/>
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +733,139 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>25,54%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>54,97%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,07%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.112619361500043</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.04087130536523445</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9276288866214318</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>1.721205173278416</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.05287994622322256</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-3,36; 8,3</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-3,38; 6,39</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,56; 4,02</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-0.9363701187942441</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2.363386353939704</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.271897850221986</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr"/>
+      <c r="G11" s="6" t="inlineStr"/>
+      <c r="H11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>4.708986539539934</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>1.482725692199687</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>8,7</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>2,67; 21,59</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-9,65; 0,0</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>0.07328659800095046</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.3024068803052918</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.1707102995098833</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.2278073481156488</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.4257530552567472</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.5144414522678666</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-18,26</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-0.6434561595874426</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.198790063507282</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.7420087191584815</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-41,82; -4,51</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.263980887972665</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.043318532835656</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.158843956040191</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr"/>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +873,203 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,32</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-1,16</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-37,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-26,97%</t>
-        </is>
-      </c>
+      <c r="C16" s="5" t="n">
+        <v>1.576240202322418</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.4605080560785582</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>inf</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-1,01; 6,45</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-4,23; 1,39</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-2,93; 1,79</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-40,62; 767,76</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-85,71; 134,07</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.4931978024530269</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.478553125910872</v>
+      </c>
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="6" t="inlineStr"/>
+      <c r="G17" s="6" t="inlineStr"/>
+      <c r="H17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>4.565759675135441</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr"/>
+      <c r="G18" s="6" t="inlineStr"/>
+      <c r="H18" s="6" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-3.608773025524188</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr"/>
+      <c r="G19" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H19" s="6" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr"/>
+      <c r="D20" s="5" t="n">
+        <v>-8.836126881383183</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="6" t="inlineStr"/>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="n">
+        <v>-0.9064114413990162</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="6" t="inlineStr"/>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.3355119272314676</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-0.264939697767726</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-0.05530106051152123</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.7019434196050487</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.3391136764266198</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.1402381285288171</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-0.3198172197310472</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-1.01087469912413</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.6073776463168</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-0.5089319136252108</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.8511366551454799</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1.023131703055062</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.3793980990978092</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0.3875376642300108</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>5.321092356535162</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>1.064038083176761</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>3.306712082467633</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1078,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
